--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,10 +897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -909,39 +907,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -971,20 +967,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -992,7 +988,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1047,8 +1043,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1057,37 +1055,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,33 +1112,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,47 +1193,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,33 +1262,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1339,8 +1343,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1349,37 +1355,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1413,16 +1421,16 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1430,7 +1438,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1447,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1480,17 +1488,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1559,11 +1567,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,7 +1631,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1640,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1674,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1699,17 +1707,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1805,19 +1813,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,7 +1850,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1851,24 +1859,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1885,12 +1893,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1918,7 +1926,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1926,7 +1934,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1951,19 +1959,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1991,17 +1999,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,3%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2039,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,33 +2069,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2097,19 +2105,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,33 +2142,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2177,12 +2185,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,33 +2215,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,7 +2288,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2289,24 +2297,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>17</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2323,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,33 +2361,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2429,17 +2437,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2502,22 +2510,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 238,9%</t>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2525,7 +2533,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2575,22 +2583,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2598,7 +2606,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2615,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,33 +2653,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2696,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2721,22 +2729,22 @@
           <t>R$ 77,00</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>31</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2744,7 +2752,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2761,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2791,33 +2799,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2864,33 +2872,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2907,12 +2915,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2937,33 +2945,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2980,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3013,22 +3021,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -3036,7 +3044,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3053,12 +3061,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3083,7 +3091,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3092,7 +3100,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3101,15 +3109,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,12 +3134,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3156,38 +3164,38 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3199,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3240,7 +3248,7 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -3272,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3305,22 +3313,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3328,7 +3336,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3345,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3384,7 +3392,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3418,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3448,12 +3456,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -3461,20 +3469,20 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3491,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3564,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3597,22 +3605,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3620,12 +3628,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3637,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3678,7 +3686,7 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -3710,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3740,33 +3748,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3783,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3824,9 +3832,9 @@
       <c r="I46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3856,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3891,20 +3899,20 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,8%</t>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3929,12 +3937,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3968,11 +3976,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4002,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4032,33 +4040,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>▲ 51,0%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4075,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4114,11 +4122,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4148,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4181,22 +4189,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4221,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4260,11 +4268,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4294,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4324,33 +4332,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,0%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4367,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4406,11 +4414,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4470,33 +4478,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4554,9 +4562,9 @@
       <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4616,25 +4624,25 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4642,7 +4650,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4692,17 +4700,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,33 +4770,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
+        <v>37</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4835,7 +4843,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4844,24 +4852,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4878,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4908,25 +4916,25 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -4951,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4984,17 +4992,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5054,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5097,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5127,33 +5135,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5170,12 +5178,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5200,38 +5208,38 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5243,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5273,33 +5281,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5316,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5346,33 +5354,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5389,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5419,33 +5427,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5462,12 +5470,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5492,33 +5500,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5535,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5565,7 +5573,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5574,11 +5582,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5587,11 +5595,11 @@
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5608,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5638,7 +5646,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5647,29 +5655,29 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 88,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5681,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5714,17 +5722,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5754,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5793,11 +5801,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5827,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5857,7 +5865,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5866,24 +5874,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5900,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5933,17 +5941,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5973,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6046,12 +6054,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6076,7 +6084,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6087,37 +6095,475 @@
       <c r="I77" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -666,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 366,7%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -816,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -889,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,39 +905,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -962,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1043,10 +1043,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1055,41 +1053,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1121,16 +1117,16 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1155,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1273,9 +1269,9 @@
       <c r="I11" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1288,7 +1284,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,14 +1378,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1417,20 +1413,20 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1455,14 +1451,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1485,7 +1481,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1493,8 +1489,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1503,39 +1501,41 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1567,24 +1567,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1642,9 +1642,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1674,14 +1674,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1707,17 +1707,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1747,14 +1747,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1786,11 +1786,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1820,14 +1820,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1850,33 +1850,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1893,14 +1893,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1926,17 +1926,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1966,14 +1966,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2005,24 +2005,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2039,14 +2039,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2069,33 +2069,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2112,14 +2112,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2145,17 +2145,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2185,14 +2185,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2233,15 +2233,15 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2251,21 +2251,21 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2288,33 +2288,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>23</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2331,14 +2331,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2364,17 +2364,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2404,14 +2404,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2434,33 +2434,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,3%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2507,33 +2507,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2550,14 +2550,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2580,33 +2580,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2623,14 +2623,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2662,16 +2662,16 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2696,14 +2696,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2726,33 +2726,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2810,9 +2810,9 @@
       <c r="I32" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,14 +2842,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2872,33 +2872,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>31</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,14 +2915,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2948,22 +2948,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 238,9%</t>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2988,14 +2988,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3018,33 +3018,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3061,14 +3061,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3091,29 +3091,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -3134,14 +3134,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3164,33 +3164,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>▲ 196,2%</t>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3246,24 +3246,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3280,14 +3280,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3310,33 +3310,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>32</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,14 +3353,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3392,11 +3392,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3426,14 +3426,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3465,16 +3465,16 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>18</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3499,14 +3499,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3572,14 +3572,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3686,9 +3686,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3718,14 +3718,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3751,17 +3751,17 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3791,14 +3791,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3830,11 +3830,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3864,14 +3864,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3894,33 +3894,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▲ 96,2%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>13</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,14 +3937,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4010,14 +4010,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4040,33 +4040,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,0%</t>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4124,9 +4124,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4156,14 +4156,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4186,33 +4186,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4229,14 +4229,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4268,11 +4268,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4302,14 +4302,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4335,22 +4335,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4375,14 +4375,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4414,11 +4414,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4448,14 +4448,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4478,33 +4478,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▲ 51,0%</t>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4521,14 +4521,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4594,14 +4594,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4624,33 +4624,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,0%</t>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4667,14 +4667,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4740,14 +4740,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4770,33 +4770,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 48,0%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4854,9 +4854,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4886,14 +4886,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4916,33 +4916,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,14 +4959,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4998,11 +4998,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5032,14 +5032,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5062,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5105,14 +5105,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5138,17 +5138,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,14 +5178,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5208,33 +5208,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
+        <v>33</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,14 +5251,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5281,33 +5281,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5324,14 +5324,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5354,25 +5354,25 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,14 +5397,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5440,20 +5440,20 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5470,14 +5470,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5543,14 +5543,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5573,33 +5573,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5616,14 +5616,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5655,29 +5655,29 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5689,14 +5689,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5719,33 +5719,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5762,14 +5762,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5801,11 +5801,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5835,14 +5835,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5865,33 +5865,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5908,14 +5908,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5941,17 +5941,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5981,14 +5981,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6020,24 +6020,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6054,14 +6054,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6084,33 +6084,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 88,9%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,14 +6127,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6200,14 +6200,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6239,24 +6239,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6314,9 +6314,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6387,9 +6387,9 @@
       <c r="I81" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6419,14 +6419,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6458,11 +6458,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6492,14 +6492,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6531,11 +6531,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6562,8 +6562,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,39 +753,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,51 +889,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1151,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1228,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>28</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1378,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1408,33 +1400,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1451,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1481,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1489,10 +1481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1501,39 +1491,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1563,20 +1551,20 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1584,7 +1572,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1601,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1631,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1639,8 +1627,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1649,37 +1639,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1704,33 +1696,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1747,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1777,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1785,47 +1777,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1850,33 +1846,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1893,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1923,7 +1919,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1931,8 +1927,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1941,37 +1939,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2005,16 +2005,16 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>28</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2072,17 +2072,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2224,24 +2224,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2297,11 +2297,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,3%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2397,19 +2397,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2443,24 +2443,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>15</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2543,19 +2543,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2583,17 +2583,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2653,33 +2653,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2726,33 +2726,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2799,33 +2799,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2881,24 +2881,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2945,33 +2945,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3027,11 +3027,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3094,22 +3094,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3173,16 +3173,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3237,33 +3237,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3313,22 +3313,22 @@
           <t>R$ 77,00</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,33 +3383,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3456,33 +3456,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,33 +3529,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3605,22 +3605,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3693,15 +3693,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3748,38 +3748,38 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4010,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4040,33 +4040,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4189,22 +4189,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4332,33 +4332,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4416,9 +4416,9 @@
       <c r="I54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4481,22 +4481,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4624,33 +4624,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4773,22 +4773,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4813,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4852,11 +4852,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4916,33 +4916,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4998,11 +4998,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5062,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>35</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5146,9 +5146,9 @@
       <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5208,25 +5208,25 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5284,17 +5284,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5354,33 +5354,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5436,24 +5436,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5500,25 +5500,25 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5543,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5646,33 +5646,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5719,33 +5719,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5792,38 +5792,38 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5865,33 +5865,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -5956,15 +5956,15 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6011,33 +6011,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
@@ -6097,20 +6097,20 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6166,11 +6166,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6179,11 +6179,11 @@
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6239,29 +6239,29 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>14</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6306,17 +6306,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6385,11 +6385,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6458,24 +6458,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6525,17 +6525,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6679,37 +6679,475 @@
       <c r="I85" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,8%</t>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1181,10 +1181,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1193,39 +1191,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1331,51 +1327,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1443,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1516,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1546,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1666,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>28</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1739,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1816,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1846,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1889,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1919,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1927,10 +1919,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1939,39 +1929,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2001,20 +1989,20 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2022,7 +2010,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2039,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2069,7 +2057,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2077,8 +2065,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2087,37 +2077,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2142,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2185,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2215,7 +2207,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2223,47 +2215,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2288,33 +2284,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2331,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2361,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2369,8 +2365,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2379,37 +2377,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>28</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2550,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2662,24 +2662,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2735,11 +2735,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,3%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2881,24 +2881,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3021,17 +3021,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3091,33 +3091,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3127,19 +3127,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3164,33 +3164,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3237,33 +3237,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3319,24 +3319,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,33 +3383,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3465,11 +3465,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3675,33 +3675,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3751,22 +3751,22 @@
           <t>R$ 77,00</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3821,33 +3821,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,33 +3894,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3967,33 +3967,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4043,22 +4043,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4131,15 +4131,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4186,38 +4186,38 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4335,22 +4335,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4448,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4478,33 +4478,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4770,33 +4770,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4854,9 +4854,9 @@
       <c r="I60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4919,22 +4919,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4998,11 +4998,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5062,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5144,11 +5144,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5211,22 +5211,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5251,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5354,33 +5354,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5436,11 +5436,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5500,33 +5500,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>35</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5584,9 +5584,9 @@
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5646,25 +5646,25 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5722,17 +5722,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5792,33 +5792,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5874,24 +5874,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5938,25 +5938,25 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -5981,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6014,17 +6014,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6084,33 +6084,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6157,33 +6157,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6230,38 +6230,38 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6303,33 +6303,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
@@ -6394,15 +6394,15 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6449,33 +6449,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6535,20 +6535,20 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6604,11 +6604,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6677,29 +6677,29 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>14</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6744,17 +6744,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6823,11 +6823,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6896,24 +6896,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6963,17 +6963,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7076,12 +7076,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7117,37 +7117,475 @@
       <c r="I91" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -957,22 +957,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -1259,20 +1259,20 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1619,10 +1619,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1631,41 +1629,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1688,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>27</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1808,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1838,33 +1834,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1881,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1911,7 +1907,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1919,8 +1915,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1929,39 +1927,41 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1984,16 +1984,16 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2002,15 +2002,15 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2027,14 +2027,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2065,10 +2065,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2077,41 +2075,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2143,16 +2139,16 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2177,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2254,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2295,9 +2291,9 @@
       <c r="I25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2310,7 +2306,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2327,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2404,14 +2400,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2439,20 +2435,20 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2477,14 +2473,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2507,7 +2503,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2515,8 +2511,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2525,39 +2523,41 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2589,24 +2589,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2664,9 +2664,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2696,14 +2696,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2729,17 +2729,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,14 +2769,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2842,14 +2842,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2872,33 +2872,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,14 +2915,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2948,17 +2948,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2988,14 +2988,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3027,24 +3027,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3061,14 +3061,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3091,33 +3091,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3134,14 +3134,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3167,17 +3167,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,3%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3255,15 +3255,15 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3310,33 +3310,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,14 +3353,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3386,17 +3386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3426,14 +3426,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3456,33 +3456,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3499,14 +3499,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3529,33 +3529,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,14 +3572,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3602,33 +3602,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3645,14 +3645,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3684,16 +3684,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3718,14 +3718,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3748,33 +3748,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>27</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3832,9 +3832,9 @@
       <c r="I46" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,14 +3864,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3894,33 +3894,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>31</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,14 +3937,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3970,22 +3970,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>57</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4010,14 +4010,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4040,33 +4040,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,14 +4083,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4113,29 +4113,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -4156,14 +4156,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4186,33 +4186,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4229,14 +4229,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4268,24 +4268,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4302,14 +4302,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4332,33 +4332,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,14 +4375,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4414,11 +4414,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4448,14 +4448,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4487,16 +4487,16 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4521,14 +4521,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4594,14 +4594,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4633,16 +4633,16 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,9 +4708,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4740,14 +4740,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4773,17 +4773,17 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4813,14 +4813,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4852,11 +4852,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4886,14 +4886,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4916,33 +4916,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,14 +4959,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5032,14 +5032,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5062,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5146,9 +5146,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,14 +5178,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5208,33 +5208,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,14 +5251,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5324,14 +5324,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5357,22 +5357,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5397,14 +5397,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5436,11 +5436,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5470,14 +5470,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5500,33 +5500,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5543,14 +5543,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5582,11 +5582,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5616,14 +5616,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5646,33 +5646,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5689,14 +5689,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5762,14 +5762,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5792,33 +5792,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5876,9 +5876,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5908,14 +5908,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5938,33 +5938,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>37</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5981,14 +5981,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6020,11 +6020,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6054,14 +6054,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6084,33 +6084,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,14 +6127,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6160,17 +6160,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6200,14 +6200,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6230,33 +6230,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6273,14 +6273,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6303,33 +6303,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6346,14 +6346,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6376,25 +6376,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6419,14 +6419,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -6462,20 +6462,20 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6492,14 +6492,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6522,25 +6522,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6565,14 +6565,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6595,33 +6595,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6638,14 +6638,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6677,29 +6677,29 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6711,14 +6711,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6741,33 +6741,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6784,14 +6784,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6823,11 +6823,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6857,14 +6857,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6887,33 +6887,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6930,14 +6930,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6963,17 +6963,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7003,14 +7003,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7042,24 +7042,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7076,14 +7076,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7106,33 +7106,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7149,14 +7149,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7222,14 +7222,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7261,24 +7261,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7336,9 +7336,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7409,9 +7409,9 @@
       <c r="I95" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7441,14 +7441,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7480,11 +7480,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7514,14 +7514,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7553,11 +7553,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7584,8 +7584,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,9 +1176,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1330,22 +1330,22 @@
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1397,20 +1397,20 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,9%</t>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1765,51 +1765,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1839,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1915,10 +1911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1927,39 +1921,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1993,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2027,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2057,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2065,8 +2057,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2075,37 +2069,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2130,33 +2126,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2173,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2250,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,33 +2276,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2323,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,7 +2349,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2361,10 +2357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2373,39 +2367,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2439,16 +2431,16 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2456,7 +2448,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2473,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2550,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2585,20 +2577,20 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2606,7 +2598,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2623,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2653,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2661,8 +2653,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2671,37 +2665,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2726,33 +2722,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2769,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2799,7 +2795,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2807,47 +2803,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2872,33 +2872,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2988,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3027,24 +3027,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3094,9 +3094,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -3134,12 +3134,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3167,17 +3167,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3255,15 +3255,15 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3310,33 +3310,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3419,19 +3419,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3465,24 +3465,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,33 +3529,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3611,11 +3611,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3675,33 +3675,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3751,22 +3751,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+        <v>17</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3791,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3821,33 +3821,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,33 +3894,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>11</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3976,16 +3976,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,6%</t>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4040,33 +4040,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4116,22 +4116,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>57</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4186,33 +4186,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4259,33 +4259,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>57</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4332,33 +4332,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>14</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4405,33 +4405,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>61</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4481,22 +4481,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4569,15 +4569,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4624,33 +4624,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,9 +4708,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4779,16 +4779,16 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4852,11 +4852,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4919,22 +4919,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5032,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5062,38 +5062,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>13</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5146,9 +5146,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5217,16 +5217,16 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5357,22 +5357,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5436,11 +5436,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5500,33 +5500,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,8%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+        <v>23</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5582,11 +5582,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5646,33 +5646,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5728,11 +5728,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5797,20 +5797,20 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,0%</t>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5835,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5874,11 +5874,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5938,33 +5938,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6020,11 +6020,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6084,33 +6084,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6166,11 +6166,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6230,33 +6230,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6306,17 +6306,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6381,20 +6381,20 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
           <t>▼ 24,2%</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
-        </is>
-      </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6460,22 +6460,22 @@
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6522,33 +6522,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6604,11 +6604,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6671,22 +6671,22 @@
           <t>R$ 25,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6711,12 +6711,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6750,24 +6750,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6814,38 +6814,38 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6896,11 +6896,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6969,24 +6969,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7042,16 +7042,16 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7076,12 +7076,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7109,17 +7109,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7182,17 +7182,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7261,24 +7261,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 88,9%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7334,24 +7334,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7401,17 +7401,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7480,11 +7480,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7553,24 +7553,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7587,12 +7587,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7660,12 +7660,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7699,11 +7699,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7730,8 +7730,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -821,20 +821,20 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,8 +889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>2</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -899,37 +901,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +958,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,47 +1039,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,22 +1111,22 @@
           <t>R$ 66,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1134,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1254,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1336,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1400,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1476,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1546,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,7 +1628,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1629,15 +1637,15 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1692,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,6%</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1984,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2057,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2057,51 +2065,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2126,7 +2130,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2135,24 +2139,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2169,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,7 +2203,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2207,10 +2211,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2219,39 +2221,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2279,17 +2279,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,33 +2422,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2503,51 +2503,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2615,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,7 +2641,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2653,10 +2649,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2665,39 +2659,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2722,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2765,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2795,7 +2787,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2803,51 +2795,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2872,25 +2860,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2898,7 +2886,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2915,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2954,11 +2942,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2981,19 +2969,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3018,33 +3006,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3061,12 +3049,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3100,11 +3088,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3127,19 +3115,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3164,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3207,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3240,17 +3228,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3273,19 +3261,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3310,33 +3298,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3353,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,33 +3371,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3419,19 +3407,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3456,33 +3444,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3499,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,7 +3517,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3538,24 +3526,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3565,19 +3553,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3602,33 +3590,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3645,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3684,7 +3672,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3748,33 +3736,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>27</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3791,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3821,55 +3809,59 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,33 +3886,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>28</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3967,55 +3959,59 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4040,33 +4036,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4113,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4156,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4186,33 +4182,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4229,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4259,55 +4255,59 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4332,33 +4332,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4405,55 +4405,59 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4478,33 +4482,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4521,12 +4525,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4551,7 +4555,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4559,8 +4563,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>18</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4569,37 +4575,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4624,33 +4632,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4667,12 +4675,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,9 +4716,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4733,19 +4741,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4770,33 +4778,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4813,12 +4821,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4852,11 +4860,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4879,19 +4887,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4916,33 +4924,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,12 +4967,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4998,7 +5006,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5025,19 +5033,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5062,38 +5070,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5105,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5138,9 +5146,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -5171,19 +5179,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5208,33 +5216,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>27</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5281,7 +5289,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5290,7 +5298,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5299,15 +5307,15 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5317,19 +5325,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5354,33 +5362,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>23</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5470,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5503,22 +5511,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5543,12 +5551,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5576,9 +5584,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -5616,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5646,33 +5654,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5689,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5719,33 +5727,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5762,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5792,33 +5800,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,8%</t>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5835,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5865,33 +5873,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5908,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5941,22 +5949,22 @@
           <t>R$ 77,00</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -5964,7 +5972,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5981,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6011,33 +6019,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>57</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6054,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6084,33 +6092,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6127,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6157,33 +6165,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6200,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6230,33 +6238,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6273,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6303,7 +6311,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6312,24 +6320,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6346,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6376,33 +6384,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6419,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6458,11 +6466,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6492,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6522,33 +6530,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6565,12 +6573,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6598,17 +6606,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6638,12 +6646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6668,25 +6676,25 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6694,7 +6702,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6711,12 +6719,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6741,7 +6749,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6750,24 +6758,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6784,12 +6792,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6814,25 +6822,25 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6840,12 +6848,12 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6857,12 +6865,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6890,17 +6898,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6930,12 +6938,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6960,25 +6968,25 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -7003,12 +7011,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7033,7 +7041,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7042,24 +7050,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7076,12 +7084,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7106,38 +7114,38 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7149,12 +7157,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7182,17 +7190,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7222,12 +7230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7252,33 +7260,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7295,12 +7303,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7325,7 +7333,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7334,24 +7342,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7368,12 +7376,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7398,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
-        </is>
-      </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7441,12 +7449,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7482,9 +7490,9 @@
       <c r="I96" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7514,12 +7522,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7544,33 +7552,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>26</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7587,12 +7595,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7626,11 +7634,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7660,12 +7668,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7690,33 +7698,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>35</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7733,12 +7741,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7772,11 +7780,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7806,12 +7814,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7836,33 +7844,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7879,12 +7887,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7918,7 +7926,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7952,78 +7960,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-013-BR</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Porta frios branco</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4025153517</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 32,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+          <t>R$ 56,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,9%</t>
-        </is>
-      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,59 +881,55 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -961,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,59 +1027,55 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 112,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>30,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1117,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1151,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1190,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>24</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 31,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1224,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1257,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1336,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1370,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1409,24 +1401,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1443,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1555,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1589,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1622,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 89,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1662,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1701,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1735,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 110,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1841,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,6%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1881,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1911,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1954,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1993,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2027,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2057,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2100,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2139,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2203,20 +2195,20 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2225,11 +2217,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2285,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2358,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>52</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2465,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2498,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2571,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 69,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,25 +2706,25 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,1%</t>
+        <v>16</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2740,7 +2732,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2787,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 89,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2796,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 583,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2830,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2860,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3088,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3195,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3228,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,8%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3371,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3380,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3414,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3444,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3487,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3526,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3560,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 175,0%</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3633,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3674,9 +3666,9 @@
       <c r="I44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3706,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3736,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3779,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3817,10 +3809,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3829,39 +3819,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3886,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3895,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3929,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4006,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4039,17 +4027,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4079,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,7 +4097,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4117,8 +4105,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4127,37 +4117,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,12 +4174,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -4195,7 +4187,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4208,7 +4200,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4225,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,7 +4247,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4263,10 +4255,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4275,39 +4265,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4332,33 +4320,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4375,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4405,7 +4393,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4413,51 +4401,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4482,33 +4466,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4525,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4555,7 +4539,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4563,51 +4547,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4632,7 +4612,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4641,24 +4621,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4675,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4714,7 +4694,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4741,19 +4721,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4787,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4862,7 +4842,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4887,19 +4867,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4927,17 +4907,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4967,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5033,19 +5013,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5070,7 +5050,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5079,24 +5059,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>11</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5113,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5146,15 +5126,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5179,19 +5159,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5225,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5259,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5289,7 +5269,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5298,7 +5278,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5307,15 +5287,15 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5325,19 +5305,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5365,17 +5345,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5478,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5508,7 +5488,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5517,24 +5497,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5551,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5584,15 +5564,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5624,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5657,17 +5637,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,3%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5727,33 +5707,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5770,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5800,25 +5780,25 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5843,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5873,33 +5853,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5916,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5946,33 +5926,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5989,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6019,33 +5999,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6062,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6092,33 +6072,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6135,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6165,33 +6145,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6208,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6241,22 +6221,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6281,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6311,33 +6291,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6354,12 +6334,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6384,25 +6364,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>20</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6410,7 +6390,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6427,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6457,7 +6437,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6466,24 +6446,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6500,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6533,22 +6513,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6556,7 +6536,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6573,12 +6553,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6612,11 +6592,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6676,33 +6656,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6719,12 +6699,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6758,7 +6738,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6792,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6822,38 +6802,38 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6865,12 +6845,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6895,7 +6875,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6903,47 +6883,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6968,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7011,12 +6995,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7041,7 +7025,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7049,8 +7033,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>2</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7059,37 +7045,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7114,33 +7102,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>▲ 96,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7157,12 +7145,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7230,12 +7218,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7260,33 +7248,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7303,12 +7291,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7333,7 +7321,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7341,47 +7329,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7406,7 +7398,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7415,16 +7407,16 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -7432,7 +7424,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7449,12 +7441,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7479,7 +7471,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7487,47 +7479,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7552,25 +7548,25 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+        <v>24</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
@@ -7595,12 +7591,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7625,7 +7621,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7633,47 +7629,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7698,33 +7698,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7807,19 +7807,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7844,33 +7844,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7887,12 +7887,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7928,9 +7928,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7953,19 +7953,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7990,33 +7990,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8072,11 +8072,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8099,19 +8099,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8136,33 +8136,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8212,17 +8212,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8245,19 +8245,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8282,33 +8282,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>27</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8355,33 +8355,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8391,19 +8391,19 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8428,33 +8428,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8471,12 +8471,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8510,24 +8510,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8574,25 +8574,25 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
@@ -8617,12 +8617,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8650,17 +8650,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8690,12 +8690,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8720,33 +8720,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8793,33 +8793,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8866,38 +8866,38 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -8909,12 +8909,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8939,33 +8939,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9021,24 +9021,24 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9055,12 +9055,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9085,33 +9085,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9161,17 +9161,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H119" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9231,33 +9231,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9304,25 +9304,25 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>▲ 88,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9395,15 +9395,15 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9450,33 +9450,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="J124" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -9566,12 +9566,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9596,33 +9596,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9712,78 +9712,3144 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-013-BR</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Porta frios branco</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4025153517</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 32,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,39 +609,41 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -662,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 56,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -808,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 56,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -884,17 +888,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -954,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +967,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1027,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 112,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1109,11 +1113,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1173,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 112,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 31,4%</t>
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1209,21 +1213,21 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1249,17 +1253,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1319,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1332,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 31,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1392,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1474,11 +1478,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1538,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1551,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1614,17 +1618,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 89,8%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1693,11 +1697,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1757,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 110,7%</t>
+          <t>▼ 89,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1839,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1903,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
+          <t>R$ 27,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>59</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1987,9 +1991,9 @@
       <c r="I21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2049,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2131,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2195,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2279,9 +2283,9 @@
       <c r="I25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2346,20 +2350,20 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 116,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2384,14 +2388,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2423,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2487,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2534,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2563,17 +2567,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2633,33 +2637,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 69,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2706,33 +2710,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2779,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 89,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 69,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 583,3%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2852,7 +2856,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2861,24 +2865,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 89,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2938,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 583,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3007,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3080,11 +3084,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3147,17 +3151,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3226,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3290,33 +3294,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>14</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3372,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3436,33 +3440,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3518,11 +3522,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3582,33 +3586,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▲ 175,0%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3664,11 +3668,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3728,33 +3732,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,9%</t>
+          <t>▲ 175,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3810,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3879,20 +3883,20 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 58,3%</t>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3947,7 +3951,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3955,10 +3959,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3967,41 +3969,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4024,33 +4024,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4144,14 +4144,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4174,33 +4174,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,14 +4217,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4255,8 +4255,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4265,39 +4267,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4320,7 +4324,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4329,24 +4333,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4404,9 +4408,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4436,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4475,11 +4479,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 55,6%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4548,11 +4552,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4621,11 +4625,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4694,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4767,11 +4771,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4840,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4907,17 +4911,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▲ 63,6%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4986,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,14 +5024,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5050,33 +5054,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▲ 63,6%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5093,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5132,11 +5136,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5166,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5196,7 +5200,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5205,24 +5209,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>11</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5239,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5278,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5312,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5351,11 +5355,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,14 +5389,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5424,7 +5428,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5458,12 +5462,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5531,12 +5535,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5572,9 +5576,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,14 +5608,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5637,17 +5641,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5681,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5716,11 +5720,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5750,14 +5754,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5780,33 +5784,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5823,14 +5827,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5862,11 +5866,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,14 +5900,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5926,33 +5930,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▲ 153,8%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5969,14 +5973,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6008,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,14 +6046,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6072,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6115,14 +6119,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6154,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6188,14 +6192,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6221,22 +6225,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6261,14 +6265,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6294,17 +6298,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6334,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6364,33 +6368,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>▲ 203,8%</t>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,14 +6411,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6437,33 +6441,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,14 +6484,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6510,12 +6514,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,9%</t>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6523,20 +6527,20 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,14 +6557,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6583,7 +6587,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6592,24 +6596,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,14 +6630,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6656,33 +6660,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,14 +6703,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6738,11 +6742,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6772,14 +6776,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6802,33 +6806,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
-        </is>
-      </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6845,14 +6849,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6875,7 +6879,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6883,10 +6887,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6895,41 +6897,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6952,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▲ 366,7%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7072,14 +7072,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7102,33 +7102,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7145,14 +7145,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7183,8 +7183,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7193,39 +7195,41 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7248,33 +7252,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7291,14 +7295,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7321,7 +7325,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7329,10 +7333,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7341,41 +7343,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7407,16 +7407,16 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -7441,12 +7441,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7518,12 +7518,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7559,9 +7559,9 @@
       <c r="I97" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7668,14 +7668,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7703,20 +7703,20 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
@@ -7741,14 +7741,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7779,8 +7779,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7789,39 +7791,41 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7844,7 +7848,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7853,24 +7857,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7887,12 +7891,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7928,9 +7932,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7960,14 +7964,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7993,17 +7997,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8033,14 +8037,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8072,11 +8076,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8106,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8136,33 +8140,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8179,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8212,17 +8216,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8252,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8282,7 +8286,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8291,24 +8295,24 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8325,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8355,33 +8359,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8398,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8431,17 +8435,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8471,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8510,7 +8514,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8519,15 +8523,15 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8537,21 +8541,21 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8574,33 +8578,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>23</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8617,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8650,17 +8654,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8690,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8720,33 +8724,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,3%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8763,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8793,33 +8797,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8836,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8866,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8909,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8948,16 +8952,16 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -8982,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9012,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9055,12 +9059,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9096,9 +9100,9 @@
       <c r="I118" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9111,7 +9115,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9128,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9158,33 +9162,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>31</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9201,14 +9205,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9234,22 +9238,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▲ 238,9%</t>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -9257,7 +9261,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9274,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9304,33 +9308,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9347,14 +9351,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9377,29 +9381,29 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -9420,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9450,33 +9454,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>▲ 196,2%</t>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9493,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9523,7 +9527,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9532,24 +9536,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9566,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9596,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>32</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9639,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9678,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9712,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9751,16 +9755,16 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>18</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
@@ -9785,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9824,7 +9828,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -9858,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9897,16 +9901,16 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
@@ -9914,12 +9918,12 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -9931,12 +9935,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9972,9 +9976,9 @@
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10004,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10037,17 +10041,17 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10065,7 +10069,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10077,14 +10081,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10116,11 +10120,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10150,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10180,33 +10184,33 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>▲ 96,2%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>13</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10223,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10262,7 +10266,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10296,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10326,33 +10330,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,0%</t>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10369,12 +10373,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10410,9 +10414,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10442,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10472,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10515,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10554,11 +10558,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10588,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10621,22 +10625,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
@@ -10661,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10700,11 +10704,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10734,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10764,33 +10768,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>▲ 51,0%</t>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10807,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10846,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10880,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10910,33 +10914,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,0%</t>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10953,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10992,7 +10996,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11026,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11056,33 +11060,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▲ 48,0%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11099,12 +11103,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11140,9 +11144,9 @@
       <c r="I146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11172,14 +11176,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11202,33 +11206,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11245,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11284,11 +11288,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11318,14 +11322,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11348,33 +11352,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11391,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11424,17 +11428,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11464,14 +11468,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11494,33 +11498,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
+        <v>33</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11537,14 +11541,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11567,33 +11571,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11610,14 +11614,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11640,25 +11644,25 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
@@ -11666,7 +11670,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11683,14 +11687,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11713,12 +11717,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
@@ -11726,20 +11730,20 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11756,14 +11760,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11786,25 +11790,25 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
@@ -11812,7 +11816,7 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11829,14 +11833,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11859,33 +11863,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11902,14 +11906,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11932,7 +11936,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11941,29 +11945,29 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -11975,14 +11979,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12005,33 +12009,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I158" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12048,14 +12052,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12087,11 +12091,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12109,7 +12113,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12121,14 +12125,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12151,33 +12155,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12194,14 +12198,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12227,17 +12231,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12267,14 +12271,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12297,7 +12301,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12306,24 +12310,24 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12340,14 +12344,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12370,33 +12374,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▲ 88,9%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12413,14 +12417,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12452,7 +12456,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12486,14 +12490,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12516,7 +12520,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12525,24 +12529,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12559,12 +12563,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12600,9 +12604,9 @@
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12632,12 +12636,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12673,9 +12677,9 @@
       <c r="I167" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12705,14 +12709,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12744,11 +12748,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12778,14 +12782,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12817,11 +12821,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12848,8 +12852,154 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -669,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -739,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +743,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,39 +755,41 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -812,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 56,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -896,9 +896,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -958,33 +958,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 56,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1034,17 +1034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1113,24 +1113,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1177,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 112,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1323,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 112,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,4%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1359,21 +1359,21 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1399,17 +1399,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1478,24 +1478,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1542,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1697,24 +1697,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1764,17 +1764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 89,8%</t>
+        <v>20</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1843,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1907,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2053,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,0%</t>
+          <t>▲ 110,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2137,9 +2137,9 @@
       <c r="I23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2199,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,14 +2242,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2281,11 +2281,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2345,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2429,9 +2429,9 @@
       <c r="I27" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2496,20 +2496,20 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2534,14 +2534,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2637,33 +2637,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>52</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2713,17 +2713,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2783,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 69,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2856,33 +2856,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>13</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2929,33 +2929,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 89,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 69,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 583,3%</t>
+        <v>37</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3011,24 +3011,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 89,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3084,24 +3084,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 583,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3230,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3264,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3297,17 +3297,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3376,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3440,33 +3440,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3522,11 +3522,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3586,33 +3586,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3668,11 +3668,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3732,33 +3732,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 175,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3878,33 +3878,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,9%</t>
+        <v>22</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 175,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,14 +3994,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4029,20 +4029,20 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4067,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4105,10 +4105,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4117,41 +4115,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4174,33 +4170,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4294,14 +4290,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4324,33 +4320,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4367,14 +4363,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4397,7 +4393,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4405,8 +4401,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4415,39 +4413,41 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4479,24 +4479,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4554,9 +4554,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4625,11 +4625,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4698,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4771,11 +4771,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4844,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4917,11 +4917,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>18</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4990,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,14 +5024,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5057,17 +5057,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,6%</t>
+        <v>17</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5136,11 +5136,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5170,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5200,33 +5200,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,6%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5243,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5282,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5355,24 +5355,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5389,14 +5389,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5428,11 +5428,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5462,14 +5462,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5501,11 +5501,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5535,14 +5535,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5608,12 +5608,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5722,9 +5722,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5754,14 +5754,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5787,17 +5787,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5827,14 +5827,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5866,11 +5866,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5900,14 +5900,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5930,33 +5930,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,1%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5973,14 +5973,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6012,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6046,14 +6046,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6076,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6119,14 +6119,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6158,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,14 +6192,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6222,33 +6222,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6265,14 +6265,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6371,22 +6371,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6411,14 +6411,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6444,17 +6444,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,14 +6484,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6514,33 +6514,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6557,14 +6557,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6587,33 +6587,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6630,14 +6630,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6660,12 +6660,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
@@ -6673,20 +6673,20 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6703,14 +6703,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6742,24 +6742,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6776,14 +6776,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6806,33 +6806,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6849,14 +6849,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6888,11 +6888,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6922,14 +6922,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6952,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
-        </is>
-      </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6995,14 +6995,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7033,10 +7033,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7045,41 +7043,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7102,33 +7098,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>27</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7145,12 +7141,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7222,14 +7218,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7252,33 +7248,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7295,14 +7291,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7325,7 +7321,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7333,8 +7329,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7343,39 +7341,41 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7398,16 +7398,16 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -7416,15 +7416,15 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7441,14 +7441,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7479,10 +7479,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7491,41 +7489,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7557,16 +7553,16 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
@@ -7591,12 +7587,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7668,12 +7664,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7709,9 +7705,9 @@
       <c r="I99" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7724,7 +7720,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,12 +7737,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7818,14 +7814,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7853,20 +7849,20 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
@@ -7891,14 +7887,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7921,7 +7917,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7929,8 +7925,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7939,39 +7937,41 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8003,24 +8003,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8078,9 +8078,9 @@
       <c r="I104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8110,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8143,17 +8143,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8183,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8222,11 +8222,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8286,33 +8286,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8329,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8362,17 +8362,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8441,24 +8441,24 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8475,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8505,33 +8505,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8548,14 +8548,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8581,17 +8581,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,3%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8621,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8669,15 +8669,15 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8687,21 +8687,21 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8724,33 +8724,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8767,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8800,17 +8800,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8840,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8870,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8913,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8943,33 +8943,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8986,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9016,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,14 +9059,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9098,16 +9098,16 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -9132,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9162,33 +9162,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>27</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9246,9 +9246,9 @@
       <c r="I120" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9278,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9308,33 +9308,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>31</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9351,14 +9351,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9384,22 +9384,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>57</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9424,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9454,33 +9454,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9497,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9527,29 +9527,29 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
@@ -9570,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9600,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9643,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9682,24 +9682,24 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9716,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9746,33 +9746,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9901,16 +9901,16 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
@@ -9935,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10008,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10047,16 +10047,16 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10122,9 +10122,9 @@
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10154,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10187,17 +10187,17 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10227,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10266,11 +10266,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10300,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10330,33 +10330,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10373,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10446,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10476,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10560,9 +10560,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10592,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10622,33 +10622,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10704,11 +10704,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10738,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10771,22 +10771,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
@@ -10811,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10914,33 +10914,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10957,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10996,11 +10996,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11060,33 +11060,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,14 +11103,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11176,14 +11176,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11206,33 +11206,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11290,9 +11290,9 @@
       <c r="I148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11322,14 +11322,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11352,33 +11352,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>37</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11395,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11434,11 +11434,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,14 +11468,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11498,33 +11498,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11541,14 +11541,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11574,17 +11574,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,14 +11614,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11644,33 +11644,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11687,14 +11687,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11717,33 +11717,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11760,14 +11760,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11790,25 +11790,25 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11833,14 +11833,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11863,12 +11863,12 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
@@ -11876,20 +11876,20 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11906,14 +11906,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11936,25 +11936,25 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11979,14 +11979,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12009,33 +12009,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12052,14 +12052,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12091,29 +12091,29 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12125,14 +12125,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12155,33 +12155,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I160" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12198,14 +12198,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12237,11 +12237,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12271,14 +12271,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12301,33 +12301,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12344,14 +12344,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12377,17 +12377,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12417,14 +12417,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12456,24 +12456,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12490,14 +12490,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12520,33 +12520,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12563,14 +12563,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -12636,14 +12636,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12675,24 +12675,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12750,9 +12750,9 @@
       <c r="I168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12823,9 +12823,9 @@
       <c r="I169" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12855,14 +12855,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12894,11 +12894,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12928,14 +12928,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12967,11 +12967,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12998,8 +12998,154 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,41 +753,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -815,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,8 +889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -903,39 +901,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -958,33 +958,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 56,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1042,9 +1042,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 56,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1180,17 +1180,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1259,24 +1259,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1323,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 112,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1469,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 112,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,4%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1505,21 +1505,21 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1545,17 +1545,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1624,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1688,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1770,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1910,17 +1910,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 89,8%</t>
+        <v>20</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2053,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2199,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,0%</t>
+          <t>▲ 110,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2283,9 +2283,9 @@
       <c r="I25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2345,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,14 +2388,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2427,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2491,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2575,9 +2575,9 @@
       <c r="I29" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2642,20 +2642,20 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2719,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2783,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>52</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2859,17 +2859,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -2929,33 +2929,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 69,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3002,33 +3002,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>13</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3075,33 +3075,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 89,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 69,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 583,3%</t>
+        <v>37</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3157,24 +3157,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 89,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3230,24 +3230,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 583,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3303,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3376,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3443,17 +3443,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3522,11 +3522,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3586,33 +3586,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3668,11 +3668,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3732,33 +3732,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3878,33 +3878,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 175,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,14 +3994,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4024,33 +4024,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,9%</t>
+        <v>22</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 175,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4067,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4106,11 +4106,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4140,14 +4140,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4175,20 +4175,20 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4213,14 +4213,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4251,10 +4251,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4263,41 +4261,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4320,33 +4316,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4440,14 +4436,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4470,33 +4466,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,14 +4509,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4543,7 +4539,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4551,8 +4547,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4561,39 +4559,41 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4625,24 +4625,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4700,9 +4700,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4771,11 +4771,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4844,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4917,11 +4917,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>8</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -4990,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,14 +5024,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5063,11 +5063,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>18</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5136,11 +5136,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5170,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5203,17 +5203,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,6%</t>
+        <v>17</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5243,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5282,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5346,33 +5346,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,6%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5389,14 +5389,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5428,11 +5428,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5462,14 +5462,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5501,24 +5501,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5535,14 +5535,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5574,11 +5574,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5608,14 +5608,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5647,11 +5647,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5681,14 +5681,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5754,12 +5754,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5827,14 +5827,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5868,9 +5868,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5900,14 +5900,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -5933,17 +5933,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5973,14 +5973,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6012,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6046,14 +6046,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6076,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,1%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6119,14 +6119,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6158,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,14 +6192,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6222,33 +6222,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6265,14 +6265,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6368,33 +6368,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6411,14 +6411,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6450,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,14 +6484,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6517,22 +6517,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,1%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6557,14 +6557,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6590,17 +6590,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6630,14 +6630,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6660,33 +6660,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6703,14 +6703,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6733,33 +6733,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6776,14 +6776,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
@@ -6819,20 +6819,20 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6849,14 +6849,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6888,24 +6888,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6922,14 +6922,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -6952,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6995,14 +6995,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7034,11 +7034,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7068,14 +7068,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7098,33 +7098,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
-        </is>
-      </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7141,14 +7141,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7179,10 +7179,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7191,41 +7189,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7248,33 +7244,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>27</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7291,12 +7287,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7368,14 +7364,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7398,33 +7394,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7441,14 +7437,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7471,7 +7467,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7479,8 +7475,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7489,39 +7487,41 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7544,16 +7544,16 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7562,15 +7562,15 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7587,14 +7587,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7625,10 +7625,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7637,41 +7635,39 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7703,16 +7699,16 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
@@ -7737,12 +7733,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7814,12 +7810,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7855,9 +7851,9 @@
       <c r="I101" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7870,7 +7866,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7887,12 +7883,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7964,14 +7960,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -7999,20 +7995,20 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
@@ -8037,14 +8033,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8067,7 +8063,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8075,8 +8071,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8085,39 +8083,41 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8149,24 +8149,24 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8183,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8224,9 +8224,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8289,17 +8289,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8329,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8368,11 +8368,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8432,33 +8432,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8475,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8508,17 +8508,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8548,14 +8548,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8587,24 +8587,24 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8621,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8651,33 +8651,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8694,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8727,17 +8727,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,3%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8767,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8815,15 +8815,15 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8833,21 +8833,21 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8870,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8913,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -8946,17 +8946,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8986,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9016,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,14 +9059,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9089,33 +9089,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9132,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9162,33 +9162,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,9%</t>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9205,14 +9205,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9244,16 +9244,16 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -9278,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9308,33 +9308,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,4%</t>
+        <v>27</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9392,9 +9392,9 @@
       <c r="I122" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9424,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9454,33 +9454,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>31</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9497,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9530,22 +9530,22 @@
           <t>R$ 63,00</t>
         </is>
       </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>57</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9570,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9600,20 +9600,20 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9622,11 +9622,11 @@
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9643,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9673,29 +9673,29 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -9716,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9746,33 +9746,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9828,24 +9828,24 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9892,33 +9892,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9935,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -9974,11 +9974,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10008,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10047,16 +10047,16 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
@@ -10081,14 +10081,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10154,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10193,16 +10193,16 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10227,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10268,9 +10268,9 @@
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10300,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10333,17 +10333,17 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10373,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10412,11 +10412,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10446,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10476,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10519,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10592,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10622,33 +10622,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10706,9 +10706,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10738,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10768,33 +10768,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10811,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10917,22 +10917,22 @@
           <t>R$ 51,00</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,8%</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
@@ -10957,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -10996,11 +10996,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11060,33 +11060,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 51,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,14 +11103,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11142,11 +11142,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11176,14 +11176,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11206,33 +11206,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11322,14 +11322,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11352,33 +11352,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11395,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11436,9 +11436,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,14 +11468,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11498,33 +11498,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>37</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11541,14 +11541,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11580,11 +11580,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,14 +11614,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11644,33 +11644,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11687,14 +11687,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11720,17 +11720,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11760,14 +11760,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11790,33 +11790,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,5%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11833,14 +11833,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11863,33 +11863,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11906,14 +11906,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -11936,25 +11936,25 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11979,14 +11979,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12009,12 +12009,12 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
@@ -12022,20 +12022,20 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12052,14 +12052,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12082,25 +12082,25 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12125,14 +12125,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12155,20 +12155,20 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12177,11 +12177,11 @@
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12198,14 +12198,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12237,29 +12237,29 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12271,14 +12271,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12301,33 +12301,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I162" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12344,14 +12344,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12383,11 +12383,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12417,14 +12417,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12447,33 +12447,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12490,14 +12490,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12523,17 +12523,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12563,14 +12563,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12602,24 +12602,24 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12636,14 +12636,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12666,33 +12666,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12709,14 +12709,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -12782,14 +12782,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -12821,24 +12821,24 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12855,14 +12855,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -12896,9 +12896,9 @@
       <c r="I170" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12969,9 +12969,9 @@
       <c r="I171" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13001,14 +13001,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-013-BR</t>
@@ -13040,11 +13040,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13074,78 +13074,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-013-BR</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Porta frios branco</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4025153517</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 32,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-013-BR-PORTA-FRIOS-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 56,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -757,11 +757,11 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,59 +881,55 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1040,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1049,15 +1045,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1067,19 +1063,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1107,22 +1103,22 @@
           <t>R$ 56,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1130,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1220,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1259,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1326,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,55 +1465,59 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 112,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1545,17 +1545,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1624,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 56,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,16 +1843,16 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1877,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1910,17 +1910,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1943,19 +1943,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 112,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,8%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2089,19 +2089,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2137,9 +2137,9 @@
       <c r="I23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,25 +2199,25 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,7%</t>
+        <v>24</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2275,17 +2275,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2427,24 +2427,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 27,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,20 +2637,20 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 89,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2659,11 +2659,11 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 116,7%</t>
+          <t>▲ 110,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2865,11 +2865,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2929,33 +2929,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 81,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>28</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3005,17 +3005,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,20 +3080,20 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 69,7%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>25</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3157,24 +3157,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 89,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 583,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3303,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3376,24 +3376,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>52</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3516,17 +3516,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,33 +3659,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 27,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 69,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3732,20 +3732,20 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 89,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3814,24 +3814,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 583,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3887,24 +3887,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4027,17 +4027,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 175,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4106,11 +4106,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4170,33 +4170,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,9%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4252,11 +4252,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4319,22 +4319,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4359,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4397,51 +4397,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4466,33 +4462,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4509,12 +4505,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4539,7 +4535,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4547,51 +4543,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4616,33 +4608,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 175,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,12 +4651,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4698,11 +4690,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,12 +4724,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,33 +4754,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,9%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,12 +4797,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4844,11 +4836,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4908,7 +4900,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4917,24 +4909,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>19</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4951,12 +4943,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4981,7 +4973,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4989,47 +4981,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5057,17 +5053,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5127,7 +5123,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5135,8 +5131,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5145,37 +5143,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5209,24 +5209,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5284,9 +5284,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5349,17 +5349,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 63,6%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5389,12 +5389,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5428,11 +5428,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5501,24 +5501,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5574,11 +5574,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5647,11 +5647,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>18</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5793,11 +5793,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5868,9 +5868,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,6%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6012,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6076,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 28,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6158,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6222,33 +6222,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,1%</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6265,12 +6265,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6368,33 +6368,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 153,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6450,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6514,33 +6514,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
-        </is>
-      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6596,11 +6596,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6630,12 +6630,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6660,33 +6660,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6736,17 +6736,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6806,33 +6806,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,8%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 28,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6888,24 +6888,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6952,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,9%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 153,8%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7034,11 +7034,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7098,33 +7098,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7180,11 +7180,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7244,33 +7244,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 67,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>25</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7317,59 +7317,55 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7397,22 +7393,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,8%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 366,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -7420,7 +7416,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7437,12 +7433,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7467,7 +7463,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 28,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7475,10 +7471,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7487,39 +7481,37 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7544,33 +7536,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,9%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7587,12 +7579,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7628,9 +7620,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7660,12 +7652,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7695,20 +7687,20 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
@@ -7716,7 +7708,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7733,12 +7725,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7763,7 +7755,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7771,10 +7763,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7783,39 +7773,37 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7840,33 +7828,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7883,12 +7871,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7960,12 +7948,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7990,33 +7978,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>28</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 366,7%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8033,12 +8021,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8110,12 +8098,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8140,33 +8128,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8183,12 +8171,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8249,19 +8237,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8286,33 +8274,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8329,12 +8317,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8359,7 +8347,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8367,47 +8355,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8432,33 +8424,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8475,12 +8467,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8505,7 +8497,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8513,8 +8505,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>1</v>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8523,37 +8517,39 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8578,25 +8574,25 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 66,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
@@ -8604,7 +8600,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8621,12 +8617,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8651,55 +8647,59 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8733,24 +8733,24 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8815,15 +8815,15 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8873,17 +8873,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8954,9 +8954,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8979,19 +8979,19 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9016,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,12 +9059,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9092,17 +9092,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9125,19 +9125,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9162,33 +9162,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 66,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,3%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9235,33 +9235,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9271,19 +9271,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9308,33 +9308,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,9%</t>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9381,33 +9381,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9417,19 +9417,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9454,33 +9454,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,4%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9527,33 +9527,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9600,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9673,33 +9673,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 238,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9746,20 +9746,20 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 59,3%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9768,11 +9768,11 @@
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9819,33 +9819,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>23</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,6%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9892,33 +9892,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 196,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>27</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,9%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9965,33 +9965,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10038,33 +10038,33 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 121,4%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10111,33 +10111,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>57</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,6%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10154,12 +10154,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10184,33 +10184,33 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10227,12 +10227,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10257,33 +10257,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 63,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>61</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 238,9%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10333,22 +10333,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,2%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10412,24 +10412,24 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10476,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+          <t>R$ 77,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 196,2%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>32</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10558,11 +10558,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10622,33 +10622,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,2%</t>
+          <t>R$ 26,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>18</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -10738,12 +10738,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10771,22 +10771,22 @@
           <t>R$ 26,00</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,0%</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
@@ -10811,12 +10811,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10852,9 +10852,9 @@
       <c r="I142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -10923,29 +10923,29 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -10996,11 +10996,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11060,20 +11060,20 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,8%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11082,11 +11082,11 @@
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11142,11 +11142,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11176,12 +11176,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11206,29 +11206,29 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 77,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>▲ 51,0%</t>
+          <t>▲ 96,2%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
@@ -11249,12 +11249,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11322,12 +11322,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11352,33 +11352,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 51,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,0%</t>
+          <t>▼ 49,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11436,9 +11436,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11498,33 +11498,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+          <t>R$ 51,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11541,12 +11541,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11580,11 +11580,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11644,33 +11644,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,8%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11726,11 +11726,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11790,29 +11790,29 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 77,00</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 51,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
@@ -11833,12 +11833,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11866,17 +11866,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11936,33 +11936,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 51,00</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 66,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11979,12 +11979,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 53,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12018,24 +12018,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12052,12 +12052,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12082,33 +12082,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 48,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12125,12 +12125,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12158,17 +12158,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12231,22 +12231,22 @@
           <t>R$ 25,00</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12310,11 +12310,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12323,11 +12323,11 @@
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12374,38 +12374,38 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12456,11 +12456,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12520,33 +12520,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 9,5%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12563,12 +12563,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 53,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12604,22 +12604,22 @@
       <c r="I166" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12636,12 +12636,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12666,33 +12666,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12742,13 +12742,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -12782,12 +12782,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12821,16 +12821,16 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▲ 88,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -12896,9 +12896,9 @@
       <c r="I170" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12907,11 +12907,11 @@
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12967,11 +12967,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13034,17 +13034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13074,12 +13074,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13113,11 +13113,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+        <v>21</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13147,12 +13147,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13186,24 +13186,24 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13220,78 +13220,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,9%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4025153517</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-013-BR</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Porta frios branco</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4042142281</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-013-BR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Porta frios branco</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4025153517</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 32,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>